--- a/Laporan_Fitur_Role_Aplikasi_Kampus.xlsx
+++ b/Laporan_Fitur_Role_Aplikasi_Kampus.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\kampus_mobile - Copy\outputs\laporan_kampus_app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dzakwanhanifkhumaini\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89F072C8-A55C-4074-B090-3B42DE06E4CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61267F4-ECA7-4395-917E-3D55CBA234A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-75" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26160" yWindow="2865" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ringkasan" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="571">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="579">
   <si>
     <t>Laporan Aplikasi Dashboard Kampus Mobile</t>
   </si>
@@ -1710,9 +1710,6 @@
     <t>Tugas Utama</t>
   </si>
   <si>
-    <t>Analisis Fitur Aplikasi</t>
-  </si>
-  <si>
     <t>Mencatat semua fitur aplikasi seperti login, dashboard, jadwal, absensi, nilai, pengajuan, polling, tagihan, event, berita, dan profil. Menjelaskan kegunaan tiap fitur.</t>
   </si>
   <si>
@@ -1720,53 +1717,6 @@
   </si>
   <si>
     <t>Analisis Role dan Akun</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Membahas role </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>admin</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>dosen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t xml:space="preserve">, dan </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>mahasiswa</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Carlito"/>
-      </rPr>
-      <t>. Menjelaskan hak akses masing-masing akun, menu yang bisa dibuka, serta perbedaan akun dummy dan akun database.</t>
-    </r>
   </si>
   <si>
     <t>Analisis Rute API</t>
@@ -1981,10 +1931,84 @@
     </r>
   </si>
   <si>
-    <t>Penyusunan dan Perapian Laporan Excel</t>
-  </si>
-  <si>
-    <t>Menggabungkan hasil kerja semua anggota, menyusun sheet Excel, merapikan format tabel, membuat ringkasan, mengecek ejaan, dan memastikan laporan mudah dibaca.</t>
+    <r>
+      <t xml:space="preserve">Membahas role </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>admin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>dosen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t xml:space="preserve">, dan </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>mahasiswa</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>. Menjelaskan hak akses masing-masing akun, menu yang bisa dibuka, serta perbedaan akun.</t>
+    </r>
+  </si>
+  <si>
+    <t>Steven Endra Saputra</t>
+  </si>
+  <si>
+    <t>BACKEND</t>
+  </si>
+  <si>
+    <t>Penyusunan dan Perapian Laporan Excel /ui/ux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehulina Anastasya Br.Tambunan </t>
+  </si>
+  <si>
+    <t>Ahmad yusuf roky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analisis Fitur Aplikasi/pembuatan ide alur aplikasi,membantu menganalisis masalah pada kode </t>
+  </si>
+  <si>
+    <t>Bunga Adelia</t>
+  </si>
+  <si>
+    <t>FRONTEND</t>
+  </si>
+  <si>
+    <t>UI/UX</t>
+  </si>
+  <si>
+    <t>QC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menggabungkan hasil kerja semua anggota, menyusun sheet Excel, merapikan format tabel, membuat ringkasan, mengecek ejaan, dan memastikan laporan mudah dibaca.serta melakukan desain untuk aplikasi </t>
   </si>
 </sst>
 </file>
@@ -2068,7 +2092,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -2097,10 +2121,88 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top style="thin">
-        <color rgb="FFD9E2EC"/>
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -2115,27 +2217,26 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
-      </bottom>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2144,6 +2245,10 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2155,15 +2260,1055 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="52">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2177,32 +3322,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelFitur" displayName="TabelFitur" ref="A4:G16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TabelFitur" displayName="TabelFitur" ref="A4:G16" headerRowDxfId="1" totalsRowDxfId="0" headerRowBorderDxfId="9" tableBorderDxfId="10">
   <autoFilter ref="A4:G16" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="No"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Fitur"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Pengguna"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Kegunaan"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Implementasi Mobile"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Endpoint/Backend"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Catatan"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="No" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Fitur" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Pengguna" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Kegunaan" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Implementasi Mobile" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Endpoint/Backend" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Catatan" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TabelRoleMenu" displayName="TabelRoleMenu" ref="A4:G7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="TabelRoleMenu" displayName="TabelRoleMenu" ref="A4:G7" headerRowDxfId="12" totalsRowDxfId="11" headerRowBorderDxfId="20" tableBorderDxfId="21">
   <autoFilter ref="A4:G7" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Role"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Akun Contoh"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Menu yang Terlihat"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Aksi Utama"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Batasan"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="File Acuan"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Penjelasan"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Role" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Akun Contoh" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Menu yang Terlihat" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Aksi Utama" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Batasan" dataDxfId="15"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="File Acuan" dataDxfId="14"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Penjelasan" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2212,46 +3357,46 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="TabelRuteAPI" displayName="TabelRuteAPI" ref="A4:G33">
   <autoFilter ref="A4:G33" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Kelompok"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Method"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Endpoint"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Role/Akses"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Controller"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Kegunaan"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Catatan"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Kelompok" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Method" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Endpoint" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Role/Akses" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Controller" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Kegunaan" dataDxfId="23"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Catatan" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="TabelAkun" displayName="TabelAkun" ref="A4:H14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="TabelAkun" displayName="TabelAkun" ref="A4:H14" headerRowDxfId="30" totalsRowDxfId="29" headerRowBorderDxfId="39" tableBorderDxfId="40">
   <autoFilter ref="A4:H14" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Sumber"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Nama"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Email"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Password"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Role"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Nomor Induk"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Jurusan/Bidang"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Keterangan"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Sumber" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Nama" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Email" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Password" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Role" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Nomor Induk" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Jurusan/Bidang" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Keterangan" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="TabelTeknologi" displayName="TabelTeknologi" ref="A4:G17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="TabelTeknologi" displayName="TabelTeknologi" ref="A4:G17" headerRowDxfId="42" totalsRowDxfId="41" headerRowBorderDxfId="50" tableBorderDxfId="51">
   <autoFilter ref="A4:G17" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Area"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Bahasa/Teknologi"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Dipakai untuk"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="File Konfigurasi"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Library/Framework"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Penjelasan Spesifik"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="Catatan"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Area" dataDxfId="49"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Bahasa/Teknologi" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Dipakai untuk" dataDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="File Konfigurasi" dataDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Library/Framework" dataDxfId="45"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Penjelasan Spesifik" dataDxfId="44"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="Catatan" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2494,322 +3639,322 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="6" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="15">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="19" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="28.5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="20">
         <v>2</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="20" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="28.5">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="20">
         <v>3</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="20" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="42.75">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="20">
         <v>20</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="20" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="28.5">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="20">
         <v>52</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="20" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="28.5">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="20">
         <v>6</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="20" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="20">
         <v>4</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="20" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="20">
         <v>1</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="20" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="G13" s="10" t="s">
+      <c r="G13" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="8" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E14" s="11" t="s">
+      <c r="E14" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="11" t="s">
+      <c r="G14" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H14" s="11" t="s">
+      <c r="H14" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="11" t="s">
+      <c r="E15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="11" t="s">
+      <c r="G15" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="11" t="s">
+      <c r="G16" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="11" t="s">
+      <c r="H16" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="11" t="s">
+      <c r="E17" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G17" s="11" t="s">
+      <c r="G17" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="9" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="G18" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="9" t="s">
         <v>28</v>
       </c>
     </row>
@@ -2839,347 +3984,347 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="6" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="38.1" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="28.5">
-      <c r="A5" s="6">
+      <c r="A5" s="13">
         <v>1</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="15" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="28.5">
-      <c r="A6" s="7">
+      <c r="A6" s="13">
         <v>2</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="15" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.5">
-      <c r="A7" s="7">
+      <c r="A7" s="13">
         <v>3</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="15" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="28.5">
-      <c r="A8" s="7">
+      <c r="A8" s="13">
         <v>4</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="15" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.5">
-      <c r="A9" s="7">
+      <c r="A9" s="13">
         <v>5</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="15" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="42.75">
-      <c r="A10" s="7">
+      <c r="A10" s="13">
         <v>6</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="15" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="42.75">
-      <c r="A11" s="7">
+      <c r="A11" s="13">
         <v>7</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="15" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.5">
-      <c r="A12" s="7">
+      <c r="A12" s="13">
         <v>8</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="15" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="28.5">
-      <c r="A13" s="7">
+      <c r="A13" s="13">
         <v>9</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="15" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="28.5">
-      <c r="A14" s="7">
+      <c r="A14" s="13">
         <v>10</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="15" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="28.5">
-      <c r="A15" s="7">
+      <c r="A15" s="13">
         <v>11</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="15" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="28.5">
-      <c r="A16" s="7">
+      <c r="A16" s="16">
         <v>12</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="18" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3210,140 +4355,140 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="6" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="38.1" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="12" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="42.75">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="15" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="42.75">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="13" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="15" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="42.75">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="18" t="s">
         <v>135</v>
       </c>
     </row>
@@ -3374,738 +4519,738 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="6" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="38.1" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="28.5">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="14" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="14" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="14" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="14" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="14" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="14" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="28.5">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="14" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="14" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="14" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="28.5">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="14" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="28.5">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="14" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="28.5">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="14" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="14" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="G18" s="7" t="s">
+      <c r="G18" s="14" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="28.5">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="G19" s="7" t="s">
+      <c r="G19" s="14" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="28.5">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="G20" s="7" t="s">
+      <c r="G20" s="14" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="28.5">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="14" t="s">
         <v>215</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="14" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="G22" s="7" t="s">
+      <c r="G22" s="14" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="28.5">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="G23" s="7" t="s">
+      <c r="G23" s="14" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="28.5">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="G24" s="7" t="s">
+      <c r="G24" s="14" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="7" t="s">
+      <c r="A25" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="G25" s="7" t="s">
+      <c r="G25" s="14" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="G26" s="7" t="s">
+      <c r="G26" s="14" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="28.5">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D27" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="G27" s="7" t="s">
+      <c r="G27" s="14" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="14" t="s">
         <v>246</v>
       </c>
-      <c r="G28" s="7" t="s">
+      <c r="G28" s="14" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="7" t="s">
+      <c r="A29" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="B29" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="G29" s="7" t="s">
+      <c r="G29" s="14" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="14" t="s">
         <v>243</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="14" t="s">
         <v>251</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="14" t="s">
         <v>252</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="14" t="s">
         <v>254</v>
       </c>
-      <c r="G30" s="7" t="s">
+      <c r="G30" s="14" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="14" t="s">
         <v>259</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="14" t="s">
         <v>260</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="G31" s="14" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="28.5">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="B32" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="14" t="s">
         <v>262</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="14" t="s">
         <v>264</v>
       </c>
-      <c r="G32" s="7" t="s">
+      <c r="G32" s="14" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="28.5">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="14" t="s">
         <v>267</v>
       </c>
-      <c r="F33" s="7" t="s">
+      <c r="F33" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="G33" s="7" t="s">
+      <c r="G33" s="14" t="s">
         <v>269</v>
       </c>
     </row>
@@ -4136,340 +5281,340 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="6" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="38.1" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="7" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="11" t="s">
         <v>273</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="11" t="s">
         <v>276</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="15" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="14" t="s">
         <v>286</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="14" t="s">
         <v>287</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="15" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="14" t="s">
         <v>292</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="14" t="s">
         <v>293</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="14" t="s">
         <v>295</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="15" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="14" t="s">
         <v>298</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="15" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="14" t="s">
         <v>304</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="14" t="s">
         <v>305</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="14" t="s">
         <v>301</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="15" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="14" t="s">
         <v>299</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="14" t="s">
         <v>310</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="15" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="13" t="s">
         <v>312</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="14" t="s">
         <v>313</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="14" t="s">
         <v>315</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="14" t="s">
         <v>283</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="15" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="13" t="s">
         <v>312</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="14" t="s">
         <v>318</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="14" t="s">
         <v>319</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="15" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="13" t="s">
         <v>312</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="14" t="s">
         <v>324</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="14" t="s">
         <v>325</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="14" t="s">
         <v>327</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="15" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="16" t="s">
         <v>312</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="17" t="s">
         <v>329</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="17" t="s">
         <v>330</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="17" t="s">
         <v>331</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="17" t="s">
         <v>299</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="17" t="s">
         <v>301</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="18" t="s">
         <v>333</v>
       </c>
     </row>
@@ -4500,370 +5645,370 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="6" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="38.1" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="42.75">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="14" t="s">
         <v>343</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="14" t="s">
         <v>344</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="14" t="s">
         <v>345</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="14" t="s">
         <v>346</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="14" t="s">
         <v>347</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="15" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="42.75">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="14" t="s">
         <v>350</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="14" t="s">
         <v>351</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="14" t="s">
         <v>353</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="14" t="s">
         <v>354</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="15" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="42.75">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="14" t="s">
         <v>357</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="14" t="s">
         <v>360</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="14" t="s">
         <v>361</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="15" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="28.5">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="13" t="s">
         <v>363</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="14" t="s">
         <v>364</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="14" t="s">
         <v>366</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="15" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.5">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="13" t="s">
         <v>368</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="14" t="s">
         <v>370</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="14" t="s">
         <v>371</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="14" t="s">
         <v>372</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="14" t="s">
         <v>373</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="15" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="28.5">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="14" t="s">
         <v>376</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="14" t="s">
         <v>377</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="14" t="s">
         <v>378</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="14" t="s">
         <v>379</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="14" t="s">
         <v>380</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="15" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="28.5">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="14" t="s">
         <v>383</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="14" t="s">
         <v>384</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="14" t="s">
         <v>385</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="14" t="s">
         <v>386</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="15" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.5">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="14" t="s">
         <v>390</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="14" t="s">
         <v>391</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="14" t="s">
         <v>392</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="14" t="s">
         <v>393</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="15" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="28.5">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="14" t="s">
         <v>396</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="14" t="s">
         <v>397</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="14" t="s">
         <v>398</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="14" t="s">
         <v>399</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="14" t="s">
         <v>400</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="15" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="42.75">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="13" t="s">
         <v>402</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="14" t="s">
         <v>403</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="14" t="s">
         <v>406</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="14" t="s">
         <v>407</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="15" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="28.5">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="13" t="s">
         <v>409</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="14" t="s">
         <v>410</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="14" t="s">
         <v>411</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="14" t="s">
         <v>412</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="14" t="s">
         <v>413</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="14" t="s">
         <v>414</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="15" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="28.5">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="13" t="s">
         <v>416</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="14" t="s">
         <v>417</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="14" t="s">
         <v>418</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="14" t="s">
         <v>419</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="14" t="s">
         <v>420</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="14" t="s">
         <v>421</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="15" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="28.5">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="16" t="s">
         <v>423</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="17" t="s">
         <v>424</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="17" t="s">
         <v>425</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="17" t="s">
         <v>426</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="17" t="s">
         <v>427</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="17" t="s">
         <v>428</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="18" t="s">
         <v>429</v>
       </c>
     </row>
@@ -4893,370 +6038,370 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>430</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="6" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="38.1" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="7" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="27.95" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="2" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="3" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="28.5">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="3" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="3" t="s">
         <v>459</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.5">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="G9" s="7" t="s">
+      <c r="G9" s="3" t="s">
         <v>465</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="28.5">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="3" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="28.5">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="F11" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="3" t="s">
         <v>478</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="28.5">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" s="3" t="s">
         <v>483</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="28.5">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="7" t="s">
+      <c r="F13" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="3" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="28.5">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="G14" s="7" t="s">
+      <c r="G14" s="3" t="s">
         <v>495</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="28.5">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="G15" s="7" t="s">
+      <c r="G15" s="3" t="s">
         <v>501</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="28.5">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="G16" s="7" t="s">
+      <c r="G16" s="3" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="28.5">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="G17" s="7" t="s">
+      <c r="G17" s="3" t="s">
         <v>513</v>
       </c>
     </row>
@@ -5286,182 +6431,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>514</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="38.1" customHeight="1">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>515</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="27.95" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="1" t="s">
         <v>520</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="42.75">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="2" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="42.75">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="3" t="s">
         <v>532</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="57">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="3" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="42.75">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="3" t="s">
         <v>542</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="28.5">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="3" t="s">
         <v>548</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="42.75">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="3" t="s">
         <v>553</v>
       </c>
     </row>
@@ -5485,93 +6630,117 @@
     <col min="1" max="1" width="31.5" customWidth="1"/>
     <col min="2" max="2" width="14.75" customWidth="1"/>
     <col min="3" max="3" width="22.125" customWidth="1"/>
-    <col min="4" max="4" width="41.625" customWidth="1"/>
-    <col min="5" max="5" width="167" customWidth="1"/>
+    <col min="4" max="4" width="82.25" customWidth="1"/>
+    <col min="5" max="5" width="176" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="5" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="B3" s="4">
+        <v>2303311028</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="B4" s="4">
+        <v>2303310836</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="13" t="s">
-        <v>554</v>
-      </c>
-      <c r="B3" s="13">
-        <v>2303311028</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>557</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>560</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13" t="s">
+      <c r="E4" s="4" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="B5" s="4">
+        <v>2303311005</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E5" s="4" t="s">
         <v>564</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13" t="s">
+    <row r="6" spans="1:5">
+      <c r="A6" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="B6" s="4">
+        <v>2303311082</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E6" s="4" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13" t="s">
-        <v>567</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>568</v>
-      </c>
-    </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13" t="s">
-        <v>569</v>
-      </c>
-      <c r="E7" s="13" t="s">
+      <c r="A7" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="B7" s="4">
+        <v>2303311048</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>570</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>578</v>
       </c>
     </row>
   </sheetData>
